--- a/Water_18O_Report.xlsx
+++ b/Water_18O_Report.xlsx
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.866694711662197</v>
+        <v>1.866694711662196</v>
       </c>
     </row>
   </sheetData>

--- a/Water_18O_Report.xlsx
+++ b/Water_18O_Report.xlsx
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.866694711662196</v>
+        <v>1.866694711662197</v>
       </c>
     </row>
   </sheetData>

--- a/Water_18O_Report.xlsx
+++ b/Water_18O_Report.xlsx
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.866694711662197</v>
+        <v>1.866694711662198</v>
       </c>
     </row>
   </sheetData>
